--- a/src/assets/Template Excel/Layout_Curing_Size.xlsx
+++ b/src/assets/Template Excel/Layout_Curing_Size.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Worktools SRI\Frontend\sri_monthly_planning_fe\src\assets\Template Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1407B238-4D76-463E-9A66-B9D6F0022F42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934E0702-82D4-47AE-9E6C-F9DED84040F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4386B32B-3324-47E2-AD2E-204A2FA7D49D}"/>
   </bookViews>
@@ -38,6 +38,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
+    <t>MACHINECURINGTYPE_ID</t>
+  </si>
+  <si>
     <t>CAPACITY</t>
   </si>
   <si>
@@ -48,9 +51,6 @@
   </si>
   <si>
     <t>SIZE</t>
-  </si>
-  <si>
-    <t>MACHINECURINGTYPE</t>
   </si>
 </sst>
 </file>
@@ -670,19 +670,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="7" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
